--- a/config/yunying/reunion_task.xlsx
+++ b/config/yunying/reunion_task.xlsx
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が1日に到達</t>
+          <t>累计登录天数达到1天</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が3日に到達</t>
+          <t>累计登录天数达到3天</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が5日に到達</t>
+          <t>累计登录天数达到5天</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が7日に到達</t>
+          <t>累计登录天数达到7天</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを20回クリア</t>
+          <t>通关20次地牢</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを50回クリア</t>
+          <t>完成50次地牢</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを100回クリア</t>
+          <t>完成100次地牢</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを180回クリア</t>
+          <t>完成180次地牢</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを260回クリア</t>
+          <t>完成260次地牢</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>アリーナで5回戦闘</t>
+          <t>在竞技场进行5次战斗</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>アリーナで10回戦闘</t>
+          <t>在竞技场进行10次战斗</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>アリーナで16回戦闘</t>
+          <t>在竞技场进行16场战斗</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>アリーナで25回戦闘</t>
+          <t>在竞技场进行25场战斗</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>アリーナで32回戦闘</t>
+          <t>32场战斗在竞技场</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を6回行う</t>
+          <t>组队进行6次伙伴挑战</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を12回行う</t>
+          <t>组队进行12次伙伴挑战</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を20回行う</t>
+          <t>组队进行20次伙伴挑战</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を32回行う</t>
+          <t>组队进行32次伙伴挑战</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を40回行う</t>
+          <t>组队进行40次伙伴挑战</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を3回行う</t>
+          <t>组队进行3次搭档挑战</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を6回行う</t>
+          <t>组队进行6次搭档挑战</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を9回行う</t>
+          <t>组队进行9次搭档挑战</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を11回行う</t>
+          <t>组队进行11次搭档挑战</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>友達になろう</t>
+          <t>交个好友吧</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
-          <t>友達登録</t>
+          <t>好友注册</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L38" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が1日に到達</t>
+          <t>累计登录天数达到1天</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="L39" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が3日に到達</t>
+          <t>累计登录天数达到3天</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="L40" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が5日に到達</t>
+          <t>累计登录天数达到5天</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="L41" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が7日に到達</t>
+          <t>累计登录天数达到7天</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="L42" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを20回クリア</t>
+          <t>通关20次地牢</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="L43" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを50回クリア</t>
+          <t>完成50次地牢</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L44" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを100回クリア</t>
+          <t>完成100次地牢</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="L45" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを180回クリア</t>
+          <t>完成180次地牢</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを260回クリア</t>
+          <t>完成260次地牢</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="L47" s="1" t="inlineStr">
         <is>
-          <t>アリーナで5回戦闘</t>
+          <t>在竞技场进行5次战斗</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
-          <t>アリーナで10回戦闘</t>
+          <t>在竞技场进行10次战斗</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="L49" s="1" t="inlineStr">
         <is>
-          <t>アリーナで16回戦闘</t>
+          <t>在竞技场进行16场战斗</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="L50" s="1" t="inlineStr">
         <is>
-          <t>アリーナで25回戦闘</t>
+          <t>在竞技场进行25场战斗</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="L51" s="1" t="inlineStr">
         <is>
-          <t>アリーナで32回戦闘</t>
+          <t>32场战斗在竞技场</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="L52" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を6回行う</t>
+          <t>组队进行6次伙伴挑战</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="L53" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を12回行う</t>
+          <t>组队进行12次伙伴挑战</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="L54" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を20回行う</t>
+          <t>组队进行20次伙伴挑战</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L55" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を32回行う</t>
+          <t>组队进行32次伙伴挑战</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="L56" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を40回行う</t>
+          <t>组队进行40次伙伴挑战</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G57" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="L57" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を3回行う</t>
+          <t>组队进行3次搭档挑战</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="L58" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を6回行う</t>
+          <t>组队进行6次搭档挑战</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="L59" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を9回行う</t>
+          <t>组队进行9次搭档挑战</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="L60" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を11回行う</t>
+          <t>组队进行11次搭档挑战</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>友達になろう</t>
+          <t>交个好友吧</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="L61" s="1" t="inlineStr">
         <is>
-          <t>友達登録</t>
+          <t>好友注册</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L72" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が1日に到達</t>
+          <t>累计登录天数达到1天</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="L73" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が3日に到達</t>
+          <t>累计登录天数达到3天</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L74" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が5日に到達</t>
+          <t>累计登录天数达到5天</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="L75" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン日数が7日に到達</t>
+          <t>累计登录天数达到7天</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="L76" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを20回クリア</t>
+          <t>通关20次地牢</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="L77" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを50回クリア</t>
+          <t>完成50次地牢</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="L78" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを100回クリア</t>
+          <t>完成100次地牢</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="L79" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを180回クリア</t>
+          <t>完成180次地牢</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="L80" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを260回クリア</t>
+          <t>完成260次地牢</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="L81" s="1" t="inlineStr">
         <is>
-          <t>アリーナで5回戦闘</t>
+          <t>在竞技场进行5次战斗</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="L82" s="1" t="inlineStr">
         <is>
-          <t>アリーナで10回戦闘</t>
+          <t>在竞技场进行10次战斗</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="L83" s="1" t="inlineStr">
         <is>
-          <t>アリーナで16回戦闘</t>
+          <t>在竞技场进行16场战斗</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L84" s="1" t="inlineStr">
         <is>
-          <t>アリーナで25回戦闘</t>
+          <t>在竞技场进行25场战斗</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>PKの王</t>
+          <t>PK之王</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="L85" s="1" t="inlineStr">
         <is>
-          <t>アリーナで32回戦闘</t>
+          <t>32场战斗在竞技场</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="L86" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を6回行う</t>
+          <t>组队进行6次伙伴挑战</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="L87" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を12回行う</t>
+          <t>组队进行12次伙伴挑战</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="L88" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を20回行う</t>
+          <t>组队进行20次伙伴挑战</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="L89" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を32回行う</t>
+          <t>组队进行32次伙伴挑战</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>お遣いの達人</t>
+          <t>花钱达人</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="L90" s="1" t="inlineStr">
         <is>
-          <t>チームを組んで仲間挑戦を40回行う</t>
+          <t>组队进行40次伙伴挑战</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="L91" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を3回行う</t>
+          <t>组队进行3次搭档挑战</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="L92" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を6回行う</t>
+          <t>组队进行6次搭档挑战</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="L93" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を9回行う</t>
+          <t>组队进行9次搭档挑战</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="L94" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を11回行う</t>
+          <t>组队进行11次搭档挑战</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>友達になろう</t>
+          <t>交个好友吧</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L95" s="1" t="inlineStr">
         <is>
-          <t>友達登録</t>
+          <t>好友注册</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="L97" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="L98" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="L99" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="L101" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L102" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="L103" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="L106" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="L107" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="L108" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="L109" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="L110" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="L111" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="L114" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="L115" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="L116" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="L117" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="L118" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="L119" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="L120" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="L122" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="L123" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="L124" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="L125" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L126" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="L127" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="L128" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="L130" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="L131" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="L132" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="L133" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="L134" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="L136" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="L138" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="L139" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L140" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="L141" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="L142" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="L143" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="L144" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="L145" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに90回挑戦</t>
+          <t>90次挑战普通地牢</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="L146" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに180回挑戦</t>
+          <t>挑战普通地牢180次</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="L147" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに270回挑戦</t>
+          <t>270次挑战普通地牢</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="L148" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに360回挑戦</t>
+          <t>360次普通地牢挑战</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="L149" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに450回挑戦</t>
+          <t>450次普通地牢挑战</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L150" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに540回挑戦</t>
+          <t>540次普通地牢挑战</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="L151" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに720回挑戦</t>
+          <t>720次挑战普通地牢</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="L152" s="1" t="inlineStr">
         <is>
-          <t>任務を6回依頼</t>
+          <t>委托任务6次</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
-          <t>任務を12回依頼</t>
+          <t>委托任务12次</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="L154" s="1" t="inlineStr">
         <is>
-          <t>任務を18回依頼</t>
+          <t>委托任务18次</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="L155" s="1" t="inlineStr">
         <is>
-          <t>任務を24回依頼</t>
+          <t>委托任务24次</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="L156" s="1" t="inlineStr">
         <is>
-          <t>任務を30回依頼</t>
+          <t>委托任务30次</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="L157" s="1" t="inlineStr">
         <is>
-          <t>任務を36回依頼</t>
+          <t>委托任务36次</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="L158" s="1" t="inlineStr">
         <is>
-          <t>任務を42回依頼</t>
+          <t>委托任务42次</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが9000に達する</t>
+          <t>时空激战Pt达到9000</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが18000に達する</t>
+          <t>时空激战Pt达到18000</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが30000に達する</t>
+          <t>时空激战Pt达到30000</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが39000に達する</t>
+          <t>时空激战Pt达到39000</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが48000に達する</t>
+          <t>时空激战Pt达到48000点</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="G164" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが57000に達する</t>
+          <t>时空激战Pt达到57000点</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="G165" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが66000に達する</t>
+          <t>时空激战Pt达到66000</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G166" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが75000に達する</t>
+          <t>时空激战Pt达到75000</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="G167" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="L167" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで3回戦闘</t>
+          <t>在公会boss中战斗3次</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="G168" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="L168" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで6回戦闘</t>
+          <t>公会boss战斗6次</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="G169" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="L169" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで9回戦闘</t>
+          <t>公会boss战斗9次</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="G170" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="L170" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで12回戦闘</t>
+          <t>公会boss战斗12次</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="G171" s="1" t="inlineStr">
         <is>
-          <t>ギルド協力</t>
+          <t>公会合作</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付10回</t>
+          <t>公会捐赠10次</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="G172" s="1" t="inlineStr">
         <is>
-          <t>ギルド協力</t>
+          <t>公会合作</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="L172" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付20回</t>
+          <t>公会捐赠20次</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="G173" s="1" t="inlineStr">
         <is>
-          <t>ギフト争奪</t>
+          <t>礼品争夺</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="L173" s="1" t="inlineStr">
         <is>
-          <t>ギルド内でギフトを5回獲得</t>
+          <t>在公会内获得5次礼物</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="G174" s="1" t="inlineStr">
         <is>
-          <t>ギフト争奪</t>
+          <t>礼品争夺</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="L174" s="1" t="inlineStr">
         <is>
-          <t>ギルド内でギフトを10回獲得</t>
+          <t>在公会内获得10次礼物</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="G175" s="1" t="inlineStr">
         <is>
-          <t>友達になろう</t>
+          <t>交个好友吧</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="L175" s="1" t="inlineStr">
         <is>
-          <t>友達登録</t>
+          <t>好友注册</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="G176" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="L176" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を1回行う</t>
+          <t>组队进行一次搭档挑战</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="G177" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="L177" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を3回行う</t>
+          <t>组队进行3次搭档挑战</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G178" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="L178" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を6回行う</t>
+          <t>组队进行6次搭档挑战</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="G179" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="L179" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を9回行う</t>
+          <t>组队进行9次搭档挑战</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="G181" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="L181" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="G182" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="L182" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="G183" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="L183" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="G184" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="L184" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="G185" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="L185" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="G186" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="L186" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="G187" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="L187" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G188" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="L188" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに90回挑戦</t>
+          <t>90次挑战普通地牢</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="G189" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="L189" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに180回挑戦</t>
+          <t>挑战普通地牢180次</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="G190" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="L190" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに270回挑戦</t>
+          <t>270次挑战普通地牢</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="G191" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="L191" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに360回挑戦</t>
+          <t>360次普通地牢挑战</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="G192" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="L192" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに450回挑戦</t>
+          <t>450次普通地牢挑战</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="G193" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="L193" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに540回挑戦</t>
+          <t>540次普通地牢挑战</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="G194" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="L194" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに720回挑戦</t>
+          <t>720次挑战普通地牢</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="G195" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="L195" s="1" t="inlineStr">
         <is>
-          <t>任務を6回依頼</t>
+          <t>委托任务6次</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G196" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="L196" s="1" t="inlineStr">
         <is>
-          <t>任務を12回依頼</t>
+          <t>委托任务12次</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="G197" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="L197" s="1" t="inlineStr">
         <is>
-          <t>任務を18回依頼</t>
+          <t>委托任务18次</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="G198" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="L198" s="1" t="inlineStr">
         <is>
-          <t>任務を24回依頼</t>
+          <t>委托任务24次</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G199" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15121,7 +15121,7 @@
       </c>
       <c r="L199" s="1" t="inlineStr">
         <is>
-          <t>任務を30回依頼</t>
+          <t>委托任务30次</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="G200" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="L200" s="1" t="inlineStr">
         <is>
-          <t>任務を36回依頼</t>
+          <t>委托任务36次</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="G201" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="L201" s="1" t="inlineStr">
         <is>
-          <t>任務を42回依頼</t>
+          <t>委托任务42次</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="G202" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが9000に達する</t>
+          <t>时空激战Pt达到9000</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="G203" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが18000に達する</t>
+          <t>时空激战Pt达到18000</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="G204" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが30000に達する</t>
+          <t>时空激战Pt达到30000</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="G205" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -15643,7 +15643,7 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが39000に達する</t>
+          <t>时空激战Pt达到39000</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="G206" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが48000に達する</t>
+          <t>时空激战Pt达到48000点</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G207" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが57000に達する</t>
+          <t>时空激战Pt达到57000点</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="G208" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが66000に達する</t>
+          <t>时空激战Pt达到66000</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="G209" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが75000に達する</t>
+          <t>时空激战Pt达到75000</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="G210" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで3回戦闘</t>
+          <t>在公会boss中战斗3次</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="G211" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="L211" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで6回戦闘</t>
+          <t>公会boss战斗6次</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="G212" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="L212" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで9回戦闘</t>
+          <t>公会boss战斗9次</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="G213" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="L213" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで12回戦闘</t>
+          <t>公会boss战斗12次</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="G214" s="1" t="inlineStr">
         <is>
-          <t>ギルド協力</t>
+          <t>公会合作</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="L214" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付10回</t>
+          <t>公会捐赠10次</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="G215" s="1" t="inlineStr">
         <is>
-          <t>ギルド協力</t>
+          <t>公会合作</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="L215" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付20回</t>
+          <t>公会捐赠20次</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="G216" s="1" t="inlineStr">
         <is>
-          <t>ギフト争奪</t>
+          <t>礼品争夺</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="L216" s="1" t="inlineStr">
         <is>
-          <t>ギルド内でギフトを5回獲得</t>
+          <t>在公会内获得5次礼物</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="G217" s="1" t="inlineStr">
         <is>
-          <t>ギフト争奪</t>
+          <t>礼品争夺</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="L217" s="1" t="inlineStr">
         <is>
-          <t>ギルド内でギフトを10回獲得</t>
+          <t>在公会内获得10次礼物</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G218" s="1" t="inlineStr">
         <is>
-          <t>友達になろう</t>
+          <t>交个好友吧</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L218" s="1" t="inlineStr">
         <is>
-          <t>友達登録</t>
+          <t>好友注册</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G219" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="L219" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を1回行う</t>
+          <t>组队进行一次搭档挑战</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="G220" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="L220" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を3回行う</t>
+          <t>组队进行3次搭档挑战</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="G221" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="L221" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を6回行う</t>
+          <t>组队进行6次搭档挑战</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="G222" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="L222" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を9回行う</t>
+          <t>组队进行9次搭档挑战</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="G224" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="L224" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="G225" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="L225" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="G226" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="L226" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -17486,7 +17486,7 @@
       </c>
       <c r="G227" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="L227" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="G228" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -17588,7 +17588,7 @@
       </c>
       <c r="L228" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="G229" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -17670,7 +17670,7 @@
       </c>
       <c r="L229" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="G230" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="L230" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="G231" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -17834,7 +17834,7 @@
       </c>
       <c r="L231" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに90回挑戦</t>
+          <t>90次挑战普通地牢</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="G232" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="L232" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに180回挑戦</t>
+          <t>挑战普通地牢180次</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="G233" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="L233" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに270回挑戦</t>
+          <t>270次挑战普通地牢</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="G234" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="L234" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに360回挑戦</t>
+          <t>360次普通地牢挑战</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="G235" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="L235" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに450回挑戦</t>
+          <t>450次普通地牢挑战</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="G236" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="L236" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに540回挑戦</t>
+          <t>540次普通地牢挑战</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="G237" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="L237" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに720回挑戦</t>
+          <t>720次挑战普通地牢</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="G238" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="L238" s="1" t="inlineStr">
         <is>
-          <t>任務を6回依頼</t>
+          <t>委托任务6次</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="G239" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="L239" s="1" t="inlineStr">
         <is>
-          <t>任務を12回依頼</t>
+          <t>委托任务12次</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="G240" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="L240" s="1" t="inlineStr">
         <is>
-          <t>任務を18回依頼</t>
+          <t>委托任务18次</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="G241" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="L241" s="1" t="inlineStr">
         <is>
-          <t>任務を24回依頼</t>
+          <t>委托任务24次</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="G242" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="L242" s="1" t="inlineStr">
         <is>
-          <t>任務を30回依頼</t>
+          <t>委托任务30次</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="G243" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="L243" s="1" t="inlineStr">
         <is>
-          <t>任務を36回依頼</t>
+          <t>委托任务36次</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="G244" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="L244" s="1" t="inlineStr">
         <is>
-          <t>任務を42回依頼</t>
+          <t>委托任务42次</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="G245" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが9000に達する</t>
+          <t>时空激战Pt达到9000</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="G246" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが18000に達する</t>
+          <t>时空激战Pt达到18000</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="G247" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが30000に達する</t>
+          <t>时空激战Pt达到30000</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="G248" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが39000に達する</t>
+          <t>时空激战Pt达到39000</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="G249" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが48000に達する</t>
+          <t>时空激战Pt达到48000点</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="G250" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが57000に達する</t>
+          <t>时空激战Pt达到57000点</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="G251" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが66000に達する</t>
+          <t>时空激战Pt达到66000</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="G252" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -19661,7 +19661,7 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが75000に達する</t>
+          <t>时空激战Pt达到75000</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="G253" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="L253" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで3回戦闘</t>
+          <t>在公会boss中战斗3次</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -19815,7 +19815,7 @@
       </c>
       <c r="G254" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="L254" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで6回戦闘</t>
+          <t>公会boss战斗6次</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="G255" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="L255" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで9回戦闘</t>
+          <t>公会boss战斗9次</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="G256" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="L256" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで12回戦闘</t>
+          <t>公会boss战斗12次</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -20076,7 +20076,7 @@
       </c>
       <c r="G257" s="1" t="inlineStr">
         <is>
-          <t>ギルド協力</t>
+          <t>公会合作</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="L257" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付10回</t>
+          <t>公会捐赠10次</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G258" s="1" t="inlineStr">
         <is>
-          <t>ギルド協力</t>
+          <t>公会合作</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="L258" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付20回</t>
+          <t>公会捐赠20次</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="G259" s="1" t="inlineStr">
         <is>
-          <t>ギフト争奪</t>
+          <t>礼品争夺</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="L259" s="1" t="inlineStr">
         <is>
-          <t>ギルド内でギフトを5回獲得</t>
+          <t>在公会内获得5次礼物</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G260" s="1" t="inlineStr">
         <is>
-          <t>ギフト争奪</t>
+          <t>礼品争夺</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20357,7 +20357,7 @@
       </c>
       <c r="L260" s="1" t="inlineStr">
         <is>
-          <t>ギルド内でギフトを10回獲得</t>
+          <t>在公会内获得10次礼物</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="G261" s="1" t="inlineStr">
         <is>
-          <t>友達になろう</t>
+          <t>交个好友吧</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="L261" s="1" t="inlineStr">
         <is>
-          <t>友達登録</t>
+          <t>好友注册</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="G262" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="L262" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を1回行う</t>
+          <t>组队进行一次搭档挑战</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="G263" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="L263" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を3回行う</t>
+          <t>组队进行3次搭档挑战</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -20725,7 +20725,7 @@
       </c>
       <c r="G264" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="L264" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を6回行う</t>
+          <t>组队进行6次搭档挑战</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -20822,7 +20822,7 @@
       </c>
       <c r="G265" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="L265" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を9回行う</t>
+          <t>组队进行9次搭档挑战</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="G267" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="L267" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="G268" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="L268" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="G269" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="G270" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="G271" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="G272" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="G273" s="1" t="inlineStr">
         <is>
-          <t>連続ログイン</t>
+          <t>连续登录</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="G274" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに90回挑戦</t>
+          <t>90次挑战普通地牢</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="G275" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21591,7 +21591,7 @@
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに180回挑戦</t>
+          <t>挑战普通地牢180次</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -21658,7 +21658,7 @@
       </c>
       <c r="G276" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに270回挑戦</t>
+          <t>270次挑战普通地牢</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="G277" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに360回挑戦</t>
+          <t>360次普通地牢挑战</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="G278" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21852,7 +21852,7 @@
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに450回挑戦</t>
+          <t>450次普通地牢挑战</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="G279" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに540回挑戦</t>
+          <t>540次普通地牢挑战</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -22006,7 +22006,7 @@
       </c>
       <c r="G280" s="1" t="inlineStr">
         <is>
-          <t>クリアの達人</t>
+          <t>透明达人</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンに720回挑戦</t>
+          <t>720次挑战普通地牢</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="G281" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -22113,7 +22113,7 @@
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
-          <t>任務を6回依頼</t>
+          <t>委托任务6次</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="G282" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
-          <t>任務を12回依頼</t>
+          <t>委托任务12次</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -22267,7 +22267,7 @@
       </c>
       <c r="G283" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
-          <t>任務を18回依頼</t>
+          <t>委托任务18次</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="G284" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
-          <t>任務を24回依頼</t>
+          <t>委托任务24次</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="G285" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
-          <t>任務を30回依頼</t>
+          <t>委托任务30次</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="G286" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="L286" s="1" t="inlineStr">
         <is>
-          <t>任務を36回依頼</t>
+          <t>委托任务36次</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="G287" s="1" t="inlineStr">
         <is>
-          <t>任務の達人</t>
+          <t>任务能手</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22635,7 +22635,7 @@
       </c>
       <c r="L287" s="1" t="inlineStr">
         <is>
-          <t>任務を42回依頼</t>
+          <t>委托任务42次</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="G288" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが9000に達する</t>
+          <t>时空激战Pt达到9000</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="G289" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが18000に達する</t>
+          <t>时空激战Pt达到18000</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="G290" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -22896,7 +22896,7 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが30000に達する</t>
+          <t>时空激战Pt达到30000</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="G291" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -22983,7 +22983,7 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが39000に達する</t>
+          <t>时空激战Pt达到39000</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="G292" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが48000に達する</t>
+          <t>时空激战Pt达到48000点</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="G293" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -23157,7 +23157,7 @@
       </c>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが57000に達する</t>
+          <t>时空激战Pt达到57000点</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="G294" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -23244,7 +23244,7 @@
       </c>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが66000に達する</t>
+          <t>时空激战Pt达到66000</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="G295" s="1" t="inlineStr">
         <is>
-          <t>時空王者</t>
+          <t>时空王者</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>時空激戦Ptが75000に達する</t>
+          <t>时空激战Pt达到75000</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="G296" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -23418,7 +23418,7 @@
       </c>
       <c r="L296" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで3回戦闘</t>
+          <t>在公会boss中战斗3次</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="G297" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -23505,7 +23505,7 @@
       </c>
       <c r="L297" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで6回戦闘</t>
+          <t>公会boss战斗6次</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -23572,7 +23572,7 @@
       </c>
       <c r="G298" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="L298" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで9回戦闘</t>
+          <t>公会boss战斗9次</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G299" s="1" t="inlineStr">
         <is>
-          <t>ギルド戦闘</t>
+          <t>公会战斗</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="L299" s="1" t="inlineStr">
         <is>
-          <t>ギルドボスで12回戦闘</t>
+          <t>公会boss战斗12次</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="G300" s="1" t="inlineStr">
         <is>
-          <t>ギルド協力</t>
+          <t>公会合作</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="L300" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付10回</t>
+          <t>公会捐赠10次</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="G301" s="1" t="inlineStr">
         <is>
-          <t>ギルド協力</t>
+          <t>公会合作</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="L301" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付20回</t>
+          <t>公会捐赠20次</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="G302" s="1" t="inlineStr">
         <is>
-          <t>ギフト争奪</t>
+          <t>礼品争夺</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="L302" s="1" t="inlineStr">
         <is>
-          <t>ギルド内でギフトを5回獲得</t>
+          <t>在公会内获得5次礼物</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="G303" s="1" t="inlineStr">
         <is>
-          <t>ギフト争奪</t>
+          <t>礼品争夺</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -24027,7 +24027,7 @@
       </c>
       <c r="L303" s="1" t="inlineStr">
         <is>
-          <t>ギルド内でギフトを10回獲得</t>
+          <t>在公会内获得10次礼物</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="G304" s="1" t="inlineStr">
         <is>
-          <t>友達になろう</t>
+          <t>交个好友吧</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="L304" s="1" t="inlineStr">
         <is>
-          <t>友達登録</t>
+          <t>好友注册</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G305" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="L305" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を1回行う</t>
+          <t>组队进行一次搭档挑战</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -24288,7 +24288,7 @@
       </c>
       <c r="G306" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -24308,7 +24308,7 @@
       </c>
       <c r="L306" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を3回行う</t>
+          <t>组队进行3次搭档挑战</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -24385,7 +24385,7 @@
       </c>
       <c r="G307" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -24405,7 +24405,7 @@
       </c>
       <c r="L307" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を6回行う</t>
+          <t>组队进行6次搭档挑战</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="G308" s="1" t="inlineStr">
         <is>
-          <t>最強の仲間</t>
+          <t>最强的伙伴</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -24502,7 +24502,7 @@
       </c>
       <c r="L308" s="1" t="inlineStr">
         <is>
-          <t>チームを組んでパートナー挑戦を9回行う</t>
+          <t>组队进行9次搭档挑战</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
